--- a/Master/4796r00/4796r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/4796r00/4796r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -934,462 +934,562 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>4.119</v>
+        <v>6.233</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2.8626</v>
+        <v>2.8453</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.0168</v>
+        <v>-1.638</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>3.22</v>
+        <v>5.234</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.9018</v>
+        <v>2.848</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-0.1799</v>
+        <v>-1.8197</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.0147</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>3.12</v>
+        <v>3.232</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.9546</v>
+        <v>2.8488</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.1574</v>
+        <v>-1.6759</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0061</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>6.221</v>
+        <v>2.229</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.0206</v>
+        <v>2.8566</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>-0.1727</v>
+        <v>-1.3859</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>6.121</v>
+        <v>4.231</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3.0218</v>
+        <v>2.8599</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.1578</v>
+        <v>-1.432</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.0126</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>5.222</v>
+        <v>4.119</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.0697</v>
+        <v>2.8626</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>-0.346</v>
+        <v>-0.0168</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.0303</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>5.122</v>
+        <v>1.23</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3.1033</v>
+        <v>2.8787</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.3304</v>
+        <v>-1.4755</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.0101</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>2.223</v>
+        <v>3.22</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>3.18</v>
+        <v>2.9018</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>-0.5759</v>
+        <v>-0.1799</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.0009</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>2.123</v>
+        <v>3.12</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3.1983</v>
+        <v>2.9546</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1574</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0042</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>1.224</v>
+        <v>6.221</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3.2232</v>
+        <v>3.0206</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>-0.7149</v>
+        <v>-0.1727</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0003</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>1.124</v>
+        <v>6.121</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3.2371</v>
+        <v>3.0218</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.7084</v>
+        <v>-0.1578</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.0021</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>4.225</v>
+        <v>5.222</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>3.2403</v>
+        <v>3.0697</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>-0.6948</v>
+        <v>-0.346</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.0007</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>4.125</v>
+        <v>5.122</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>3.2571</v>
+        <v>3.1033</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.6965</v>
+        <v>-0.3304</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0069</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>3.226</v>
+        <v>2.223</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.2632</v>
+        <v>3.18</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-0.8603</v>
+        <v>-0.5759</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0065</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>3.126</v>
+        <v>2.123</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3.2917</v>
+        <v>3.1983</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.8652</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0055</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>6.127</v>
+        <v>1.224</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>3.2996</v>
+        <v>3.2232</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-0.8442</v>
+        <v>-0.7149</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0061</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>5.228</v>
+        <v>1.124</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3.3219</v>
+        <v>3.2371</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-1.0526</v>
+        <v>-0.7084</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0013</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>5.128</v>
+        <v>4.225</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3.3226</v>
+        <v>3.2403</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-1.0254</v>
+        <v>-0.6948</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0053</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>1.23</v>
+        <v>4.125</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3.3461</v>
+        <v>3.2571</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-1.4634</v>
+        <v>-0.6965</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>1.13</v>
+        <v>3.226</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3.3627</v>
+        <v>3.2632</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-1.4601</v>
+        <v>-0.8603</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0023</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>2.129</v>
+        <v>3.126</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3.3631</v>
+        <v>3.2917</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-1.3202</v>
+        <v>-0.8652</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0032</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
+        <v>6.127</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>3.2996</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>-0.8442</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0.0061</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>5.228</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>3.3219</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>-1.0526</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.0013</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>5.128</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>3.3226</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>-1.0254</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0.0053</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>3.3627</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>-1.4601</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.0023</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>2.129</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>3.3631</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>-1.3202</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
         <v>4.131</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B51" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="n">
+      <c r="C51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="n">
         <v>3.3657</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E51" s="7" t="n">
         <v>-1.4092</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F51" s="7" t="n">
         <v>0.0003</v>
       </c>
     </row>
-    <row r="48">
-      <c r="E48" s="8" t="inlineStr">
+    <row r="53">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F48" s="9" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="E49" s="8" t="inlineStr">
+      <c r="F53" s="9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>0.8048999999999999</v>
+      <c r="F54" s="10" t="n">
+        <v>0.8109</v>
       </c>
     </row>
   </sheetData>
